--- a/Pruebas/Archivos/Template/Ecuador/Template_HRC_oxxo_1.xlsx
+++ b/Pruebas/Archivos/Template/Ecuador/Template_HRC_oxxo_1.xlsx
@@ -700,7 +700,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>30/10/2025</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">

--- a/Pruebas/Archivos/Template/Ecuador/Template_HRC_oxxo_1.xlsx
+++ b/Pruebas/Archivos/Template/Ecuador/Template_HRC_oxxo_1.xlsx
@@ -624,11 +624,7 @@
           <t>Cliente</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>CADENA COML OXXO COLOMBIA S A</t>
-        </is>
-      </c>
+      <c r="D6" s="4" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr">
         <is>
           <t>TOTAL s/ BANCOS</t>
@@ -656,9 +652,7 @@
           <t>Codigo de Cliente</t>
         </is>
       </c>
-      <c r="D8" s="4" t="n">
-        <v>30390369</v>
-      </c>
+      <c r="D8" s="4" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr">
         <is>
           <t>DIFERENCIA</t>
@@ -700,7 +694,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
